--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保策略表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保策略表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,11 +513,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -564,11 +560,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -948,6 +940,108 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>按华为标准保修政策</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3 年 服务器介质保留服务</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>按华为标准保修政策</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3 年 Hi-Care高级服务</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保策略表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保策略表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,11 +983,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -1034,14 +1030,112 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>按华为标准保修政策</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3 年 服务器介质保留服务</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>按华为标准保修政策</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3 年 Hi-Care高级服务</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保策略表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保策略表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -560,7 +564,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1077,11 +1085,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1128,14 +1132,104 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>按华为标准保修政策</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3 年 服务器介质保留服务</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>按华为标准保修政策</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3 年 Hi-Care高级服务</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2029-12-12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
